--- a/app/reports/EMBC_research.xlsx
+++ b/app/reports/EMBC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.08</v>
+        <v>5.1</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04644999980926514</v>
+        <v>0.04696000099182129</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>56659596.8503937</v>
+        <v>56659601.56862745</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>5.08</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>287830752</v>
+        <v>288963968</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>5.53</v>
+        <v>5.6</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="6">
@@ -1532,14 +1532,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>543465408</v>
+        <v>533424512</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>-8.782999999999999</v>
+        <v>-9.462999999999999</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>9.669</v>
+        <v>9.132999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>2409262848</v>
+        <v>2344594944</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>22.389423</v>
+        <v>21.788462</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>168.355</v>
+        <v>160.074</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4.569</v>
+        <v>4.345</v>
       </c>
     </row>
     <row r="8">
@@ -1578,14 +1578,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>237139184</v>
+        <v>235344624</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>2.934</v>
+        <v>2.943</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>0.885</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="9">
@@ -1600,14 +1600,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>485024544</v>
+        <v>529117664</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>21.728</v>
+        <v>22.672</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.632</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="10">
@@ -1622,14 +1622,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>2161037056</v>
+        <v>2111038848</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-58.756</v>
+        <v>-58.152</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>5.557</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="11">
@@ -1644,14 +1644,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>307513600</v>
+        <v>289818432</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.414</v>
+        <v>-1.243</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.284</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12">
@@ -1666,14 +1666,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>574148480</v>
+        <v>560454464</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>-3.102</v>
+        <v>-2.999</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>144.046</v>
+        <v>139.242</v>
       </c>
     </row>
     <row r="13">
@@ -1688,14 +1688,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1516558208</v>
+        <v>1499470208</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-12.84</v>
+        <v>-12.666</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>19.276</v>
+        <v>19.016</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/EMBC_research.xlsx
+++ b/app/reports/EMBC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-16 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/EMBC_research.xlsx
+++ b/app/reports/EMBC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-16 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-18 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.1</v>
+        <v>5.115</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.04711999893188477</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>56659601.56862745</v>
+        <v>56659600.39100684</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>5.1</v>
+        <v>5.115</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>288963968</v>
+        <v>289813856</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>5.6</v>
@@ -1532,14 +1532,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>533424512</v>
+        <v>545348096</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>-9.462999999999999</v>
+        <v>-9.558999999999999</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>9.132999999999999</v>
+        <v>9.226000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>2344594944</v>
+        <v>2347440384</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>21.788462</v>
+        <v>21.814905</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>160.074</v>
+        <v>164.485</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4.345</v>
+        <v>4.464</v>
       </c>
     </row>
     <row r="8">
@@ -1582,10 +1582,10 @@
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>2.943</v>
+        <v>2.923</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>0.888</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="9">
@@ -1600,14 +1600,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>529117664</v>
+        <v>503679328</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>22.672</v>
+        <v>22.172</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.66</v>
+        <v>0.645</v>
       </c>
     </row>
     <row r="10">
@@ -1622,14 +1622,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>2111038848</v>
+        <v>2094372864</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-58.152</v>
+        <v>-58.001</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>5.5</v>
+        <v>5.485</v>
       </c>
     </row>
     <row r="11">
@@ -1644,14 +1644,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>289818432</v>
+        <v>275949248</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.243</v>
+        <v>-1.26</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.25</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="12">
@@ -1666,14 +1666,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>560454464</v>
+        <v>550478784</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>-2.999</v>
+        <v>-3.074</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>139.242</v>
+        <v>142.736</v>
       </c>
     </row>
     <row r="13">
@@ -1688,14 +1688,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1499470208</v>
+        <v>1485052160</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-12.666</v>
+        <v>-12.513</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>19.016</v>
+        <v>18.786</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/EMBC_research.xlsx
+++ b/app/reports/EMBC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-18 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-19 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.115</v>
+        <v>5.415</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04711999893188477</v>
+        <v>0.04674000263214111</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>56659600.39100684</v>
+        <v>56659601.84672207</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>5.115</v>
+        <v>5.415</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>289813856</v>
+        <v>306811744</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>5.6</v>
@@ -1532,14 +1532,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>545348096</v>
+        <v>583880192</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>-9.558999999999999</v>
+        <v>-9.631</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>9.226000000000001</v>
+        <v>9.295</v>
       </c>
     </row>
     <row r="7">
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>2347440384</v>
+        <v>2447028736</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>21.814905</v>
+        <v>22.740385</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>164.485</v>
+        <v>163.653</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4.464</v>
+        <v>4.442</v>
       </c>
     </row>
     <row r="8">
@@ -1578,14 +1578,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>235344624</v>
+        <v>248675680</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>2.923</v>
+        <v>2.958</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>0.882</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="9">
@@ -1600,14 +1600,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>503679328</v>
+        <v>511028192</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>22.172</v>
+        <v>22.487</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.645</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="10">
@@ -1622,14 +1622,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>2094372864</v>
+        <v>2595466752</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-58.001</v>
+        <v>-58.454</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>5.485</v>
+        <v>5.528</v>
       </c>
     </row>
     <row r="11">
@@ -1644,14 +1644,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>275949248</v>
+        <v>292687904</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.26</v>
+        <v>-1.106</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.253</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="12">
@@ -1666,14 +1666,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>550478784</v>
+        <v>619583360</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>-3.074</v>
+        <v>-2.961</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>142.736</v>
+        <v>137.495</v>
       </c>
     </row>
     <row r="13">
@@ -1688,14 +1688,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1485052160</v>
+        <v>1673554048</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-12.513</v>
+        <v>-12.533</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>18.786</v>
+        <v>18.816</v>
       </c>
     </row>
     <row r="15">
